--- a/output/pdf_financials_xlsx/RKV.xlsx
+++ b/output/pdf_financials_xlsx/RKV.xlsx
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006077</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>-0.025448</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.190934</v>
+        <v>-0.197011</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>-0.025448</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.190934</v>
+        <v>-0.197011</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">

--- a/output/pdf_financials_xlsx/RKV.xlsx
+++ b/output/pdf_financials_xlsx/RKV.xlsx
@@ -619,10 +619,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.000185</v>
+        <v>0.005448</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7.1e-05</v>
+        <v>0.03354</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -8566,7 +8566,11 @@
           <t>Proceeds from private placement 8</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -12862,7 +12866,11 @@
           <t>Rent and office expenses 8</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>0.005263</v>
       </c>
